--- a/tc/공지사항_TC_2026-09_v1.xlsx
+++ b/tc/공지사항_TC_2026-09_v1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="149">
   <si>
     <t>No.</t>
   </si>
@@ -308,19 +308,62 @@
     <t>1. 목록에서 공지 카드 선택</t>
   </si>
   <si>
-    <t>1. 해당 공지 상세 페이지로 이동됨</t>
-  </si>
-  <si>
-    <t>날짜 표기</t>
+    <t>1. 해당 공지 상세 페이지로 이동됨 (URL: /notice/{id})</t>
+  </si>
+  <si>
+    <t>상단 라벨</t>
   </si>
   <si>
     <t>1. 공지 상세 진입</t>
   </si>
   <si>
-    <t>1. 상세 페이지 날짜 확인</t>
-  </si>
-  <si>
-    <t>1. 목록과 동일한 날짜 표기(formatNoticePeriod) — 라벨 없이 날짜(범위), 만료일 없으면 등록일만</t>
+    <t>1. 상세 상단 라벨 확인</t>
+  </si>
+  <si>
+    <t>1. 상단 라벨 "SMARTSCORE 공지사항" 노출</t>
+  </si>
+  <si>
+    <t>1. 상세 카테고리 배지 확인</t>
+  </si>
+  <si>
+    <t>1. 카테고리(솔루션) 배지 노출 (예: "전체")</t>
+  </si>
+  <si>
+    <t>1. 상세 제목 확인</t>
+  </si>
+  <si>
+    <t>1. 공지 제목 노출 (예: "(시험) URL 토큰 표본 공지")</t>
+  </si>
+  <si>
+    <t>1. 게시 만료일이 설정된 공지 상세</t>
+  </si>
+  <si>
+    <t>1. 상세 날짜 확인</t>
+  </si>
+  <si>
+    <t>1. "등록일 ~ 게시만료일" 범위 노출 (목록과 동일 formatNoticePeriod)</t>
+  </si>
+  <si>
+    <t>날짜 — 무기한</t>
+  </si>
+  <si>
+    <t>1. 게시 만료일이 없는(무기한) 공지 상세</t>
+  </si>
+  <si>
+    <t>1. 등록일만 노출, "무기한" 텍스트 미표기</t>
+  </si>
+  <si>
+    <t>날짜 라벨/시간대</t>
+  </si>
+  <si>
+    <t>1. 상세 날짜 표기 형식 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. "등록:" 등 접두 라벨 없이 날짜(범위)만
+2. KST 기준(현재 국가별 환산 없이 KST 원본 + "KST" 라벨 임시)</t>
+  </si>
+  <si>
+    <t>미해결: 국가별 현지시간 환산 보류(ISSUE-079) - 기획 확인 필요</t>
   </si>
   <si>
     <t>본문 렌더</t>
@@ -342,7 +385,7 @@
     <t>1. 본문 내 URL 확인</t>
   </si>
   <si>
-    <t>1. 본문 URL이 클릭 가능한 링크로 자동 렌더링됨</t>
+    <t>1. 본문 URL이 클릭 가능한 링크(a[href^="http"])로 자동 렌더링됨</t>
   </si>
   <si>
     <t>이미지 라이트박스</t>
@@ -358,7 +401,11 @@
   </si>
   <si>
     <t xml:space="preserve">1. 이미지가 확대(라이트박스) 노출됨 (조회 시점에만 적용)
-2. 배경 클릭 / 닫기 / Esc 로 닫힘</t>
+2. 공지 본문 이미지는 단일 확대 — 좌우 화살표 미제공
+3. 배경 클릭 / 닫기 / Esc 로 닫힘</t>
+  </si>
+  <si>
+    <t>2장 이상 좌우 넘겨보기는 문의 스레드 이미지에만 적용 — 공지 본문 이미지는 단일 확대</t>
   </si>
   <si>
     <t>원문 토글</t>
@@ -373,7 +420,7 @@
     <t>뒤로가기</t>
   </si>
   <si>
-    <t>1. 뒤로가기 수행</t>
+    <t>1. [공지사항 목록] 버튼 선택</t>
   </si>
   <si>
     <t>1. 공지사항 목록으로 복귀</t>
@@ -846,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1646,7 +1693,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>26</v>
@@ -1655,10 +1702,10 @@
         <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>22</v>
@@ -1681,19 +1728,19 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>22</v>
@@ -1716,19 +1763,19 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>22</v>
@@ -1751,19 +1798,19 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>22</v>
@@ -1786,19 +1833,19 @@
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>22</v>
@@ -1810,7 +1857,7 @@
         <v>23</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -1819,23 +1866,21 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>22</v>
@@ -1858,19 +1903,19 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>22</v>
@@ -1891,35 +1936,33 @@
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -1928,39 +1971,218 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="J32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="F33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" s="2" t="s">
+      <c r="I33" s="2" t="s">
         <v>133</v>
       </c>
+      <c r="J33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M31"/>
+  <autoFilter ref="A2:M36"/>
   <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A1:A2"/>
@@ -1972,14 +2194,14 @@
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="B3:B31"/>
-    <mergeCell ref="C3:C31"/>
+    <mergeCell ref="B3:B36"/>
+    <mergeCell ref="C3:C36"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="D13:D20"/>
-    <mergeCell ref="D21:D27"/>
-    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D21:D32"/>
+    <mergeCell ref="D33:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
